--- a/Robot/АЛКУ_СВОДКА.xlsx
+++ b/Robot/АЛКУ_СВОДКА.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dmbog\Рабочий стол\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\SW001-ALKU\Robot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65F52ED0-AB4F-45BA-BEFB-3964F6BDEAE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42F52439-260F-4D22-8C55-703779E6DA8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{59D0C2ED-A381-469C-98D8-E3CEFE125B51}"/>
+    <workbookView xWindow="13080" yWindow="0" windowWidth="10056" windowHeight="12336" xr2:uid="{59D0C2ED-A381-469C-98D8-E3CEFE125B51}"/>
   </bookViews>
   <sheets>
     <sheet name="Общий графсет" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="101">
   <si>
     <t>Графсеты проекта АЛКУ</t>
   </si>
@@ -325,6 +325,21 @@
   </si>
   <si>
     <t>ETALON</t>
+  </si>
+  <si>
+    <t>Очистить тару отбраковки</t>
+  </si>
+  <si>
+    <t>CLEANDEFECT</t>
+  </si>
+  <si>
+    <t>Датчик позиционера полный</t>
+  </si>
+  <si>
+    <t>Завершение программы</t>
+  </si>
+  <si>
+    <t>Пауза</t>
   </si>
 </sst>
 </file>
@@ -405,33 +420,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -443,10 +437,28 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -783,7 +795,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16984AE6-47A2-4200-8C2D-12013DD9AE58}">
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -797,40 +809,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="G2" s="2" t="s">
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="G2" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="H2" s="2"/>
+      <c r="H2" s="7"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="G3" s="3" t="s">
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="G3" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="H3" s="3"/>
+      <c r="H3" s="6"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
@@ -929,10 +941,10 @@
       <c r="B10" t="s">
         <v>27</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="H10" s="4"/>
+      <c r="H10" s="8"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11">
@@ -1024,111 +1036,111 @@
         <v>79</v>
       </c>
     </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>105</v>
+      </c>
+      <c r="B20" t="s">
+        <v>100</v>
+      </c>
+    </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+      <c r="A21">
+        <v>255</v>
+      </c>
+      <c r="B21" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
         <v>2</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B24" t="s">
         <v>3</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C24" t="s">
         <v>4</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D24" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23">
-        <v>0</v>
-      </c>
-      <c r="B23" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24">
-        <v>1</v>
-      </c>
-      <c r="B24" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B25" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B26" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B27" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B28" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B29" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="B30" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>101</v>
+        <v>6</v>
       </c>
       <c r="B31" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B32" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B33" t="s">
         <v>78</v>
@@ -1136,21 +1148,53 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34">
+        <v>102</v>
+      </c>
+      <c r="B34" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <v>103</v>
+      </c>
+      <c r="B35" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36">
         <v>104</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B36" t="s">
         <v>79</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37">
+        <v>105</v>
+      </c>
+      <c r="B37" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38">
+        <v>255</v>
+      </c>
+      <c r="B38" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A23:D23"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="G3:H3"/>
     <mergeCell ref="G10:H10"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1161,128 +1205,128 @@
   <dimension ref="A1:N75"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.21875" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="1.5546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.21875" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="1.5546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="1.5546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.5546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="1.5546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.44140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="1.5546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.44140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="1.5546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.44140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="1.5546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.88671875" style="6"/>
+    <col min="1" max="1" width="29.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="1.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="1.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="1.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="1.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="1.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="1.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="5"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
+      <c r="L1" s="11"/>
+      <c r="M1" s="11"/>
+      <c r="N1" s="11"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="8" t="s">
+      <c r="B2" s="2"/>
+      <c r="C2" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
-      <c r="M2" s="8"/>
-      <c r="N2" s="8"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="12"/>
+      <c r="M2" s="12"/>
+      <c r="N2" s="12"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9" t="s">
+      <c r="B3" s="13"/>
+      <c r="C3" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9" t="s">
+      <c r="D3" s="13"/>
+      <c r="E3" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9" t="s">
+      <c r="F3" s="13"/>
+      <c r="G3" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9" t="s">
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
-      <c r="N3" s="9"/>
+      <c r="L3" s="13"/>
+      <c r="M3" s="13"/>
+      <c r="N3" s="13"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4" s="6" t="s">
+      <c r="B4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" s="6">
+      <c r="D4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" s="1">
         <v>240</v>
       </c>
-      <c r="F4" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="G4" s="6">
+      <c r="F4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4" s="1">
         <v>5</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="I4" s="6">
+      <c r="I4" s="1">
         <v>6</v>
       </c>
-      <c r="J4" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="K4" s="6">
+      <c r="J4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K4" s="1">
         <v>5</v>
       </c>
-      <c r="L4" s="6" t="s">
+      <c r="L4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M4" s="6">
+      <c r="M4" s="1">
         <v>6</v>
       </c>
-      <c r="N4" s="6" t="s">
+      <c r="N4" s="1" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1303,93 +1347,93 @@
       <c r="N5" s="10"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="1" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" s="6" t="s">
+      <c r="B7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E7" s="6" t="s">
+      <c r="D7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" s="6" t="s">
+      <c r="B8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E8" s="6" t="s">
+      <c r="D8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" s="6" t="s">
+      <c r="B9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E9" s="6" t="s">
+      <c r="D9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" s="11" t="s">
+      <c r="B10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D10" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E10" s="6" t="s">
+      <c r="D10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F10" s="1" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1410,24 +1454,24 @@
       <c r="N11" s="10"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="1" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" s="6">
+      <c r="B13" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="1">
         <v>90</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="1" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1448,42 +1492,42 @@
       <c r="N14" s="10"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E15" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G15" s="6" t="s">
+      <c r="G15" s="1" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" s="6" t="s">
+      <c r="B16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D16" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E16" s="6" t="s">
+      <c r="D16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="F16" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="G16" s="6">
+      <c r="F16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G16" s="1">
         <v>180</v>
       </c>
-      <c r="H16" s="6" t="s">
+      <c r="H16" s="1" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1504,15 +1548,15 @@
       <c r="N17" s="10"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="1" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="1" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1533,15 +1577,15 @@
       <c r="N20" s="10"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="1" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="6" t="s">
+      <c r="A22" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="1" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1562,15 +1606,15 @@
       <c r="N23" s="10"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="1" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="6" t="s">
+      <c r="A25" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="1" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1591,15 +1635,15 @@
       <c r="N26" s="10"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="1" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="6" t="s">
+      <c r="A28" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="1" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1620,15 +1664,15 @@
       <c r="N29" s="10"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="6" t="s">
+      <c r="A30" s="1" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="6" t="s">
+      <c r="A31" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="B31" s="1" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1649,15 +1693,15 @@
       <c r="N32" s="10"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="6" t="s">
+      <c r="A33" s="1" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="6" t="s">
+      <c r="A34" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="1" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1678,15 +1722,15 @@
       <c r="N35" s="10"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="6" t="s">
+      <c r="A36" s="1" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="6" t="s">
+      <c r="A37" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="B37" s="1" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1707,134 +1751,134 @@
       <c r="N38" s="10"/>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="12"/>
-      <c r="B39" s="12"/>
-      <c r="C39" s="12"/>
-      <c r="D39" s="12"/>
-      <c r="E39" s="12"/>
-      <c r="F39" s="12"/>
-      <c r="G39" s="12" t="s">
+      <c r="A39" s="5"/>
+      <c r="B39" s="5"/>
+      <c r="C39" s="5"/>
+      <c r="D39" s="5"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="5"/>
+      <c r="G39" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="H39" s="12"/>
-      <c r="I39" s="12" t="s">
+      <c r="H39" s="5"/>
+      <c r="I39" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="J39" s="12"/>
-      <c r="K39" s="12" t="s">
+      <c r="J39" s="5"/>
+      <c r="K39" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="L39" s="12"/>
-      <c r="M39" s="12" t="s">
+      <c r="L39" s="5"/>
+      <c r="M39" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="N39" s="12"/>
+      <c r="N39" s="5"/>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="5" t="s">
+      <c r="A41" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="B41" s="5"/>
-      <c r="C41" s="5"/>
-      <c r="D41" s="5"/>
-      <c r="E41" s="5"/>
-      <c r="F41" s="5"/>
-      <c r="G41" s="5"/>
-      <c r="H41" s="5"/>
-      <c r="I41" s="5"/>
-      <c r="J41" s="5"/>
-      <c r="K41" s="5"/>
-      <c r="L41" s="5"/>
-      <c r="M41" s="5"/>
-      <c r="N41" s="5"/>
+      <c r="B41" s="11"/>
+      <c r="C41" s="11"/>
+      <c r="D41" s="11"/>
+      <c r="E41" s="11"/>
+      <c r="F41" s="11"/>
+      <c r="G41" s="11"/>
+      <c r="H41" s="11"/>
+      <c r="I41" s="11"/>
+      <c r="J41" s="11"/>
+      <c r="K41" s="11"/>
+      <c r="L41" s="11"/>
+      <c r="M41" s="11"/>
+      <c r="N41" s="11"/>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A42" s="7" t="s">
+      <c r="A42" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B42" s="7"/>
-      <c r="C42" s="8" t="s">
+      <c r="B42" s="2"/>
+      <c r="C42" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="8"/>
-      <c r="G42" s="8"/>
-      <c r="H42" s="8"/>
-      <c r="I42" s="8"/>
-      <c r="J42" s="8"/>
-      <c r="K42" s="8"/>
-      <c r="L42" s="8"/>
-      <c r="M42" s="8"/>
-      <c r="N42" s="8"/>
+      <c r="D42" s="12"/>
+      <c r="E42" s="12"/>
+      <c r="F42" s="12"/>
+      <c r="G42" s="12"/>
+      <c r="H42" s="12"/>
+      <c r="I42" s="12"/>
+      <c r="J42" s="12"/>
+      <c r="K42" s="12"/>
+      <c r="L42" s="12"/>
+      <c r="M42" s="12"/>
+      <c r="N42" s="12"/>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A43" s="9" t="s">
+      <c r="A43" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="B43" s="9"/>
-      <c r="C43" s="9" t="s">
+      <c r="B43" s="13"/>
+      <c r="C43" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="9"/>
-      <c r="E43" s="9" t="s">
+      <c r="D43" s="13"/>
+      <c r="E43" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="F43" s="9"/>
-      <c r="G43" s="9" t="s">
+      <c r="F43" s="13"/>
+      <c r="G43" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="H43" s="9"/>
-      <c r="I43" s="9"/>
-      <c r="J43" s="9"/>
-      <c r="K43" s="9" t="s">
+      <c r="H43" s="13"/>
+      <c r="I43" s="13"/>
+      <c r="J43" s="13"/>
+      <c r="K43" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="L43" s="9"/>
-      <c r="M43" s="9"/>
-      <c r="N43" s="9"/>
+      <c r="L43" s="13"/>
+      <c r="M43" s="13"/>
+      <c r="N43" s="13"/>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A44" s="6" t="s">
+      <c r="A44" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B44" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C44" s="6" t="s">
+      <c r="B44" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C44" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D44" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E44" s="6">
+      <c r="D44" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E44" s="1">
         <v>240</v>
       </c>
-      <c r="F44" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="G44" s="6">
+      <c r="F44" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G44" s="1">
         <v>5</v>
       </c>
-      <c r="H44" s="6" t="s">
+      <c r="H44" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="I44" s="6">
+      <c r="I44" s="1">
         <v>6</v>
       </c>
-      <c r="J44" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="K44" s="6">
+      <c r="J44" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K44" s="1">
         <v>5</v>
       </c>
-      <c r="L44" s="6" t="s">
+      <c r="L44" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M44" s="6">
+      <c r="M44" s="1">
         <v>6</v>
       </c>
-      <c r="N44" s="6" t="s">
+      <c r="N44" s="1" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1855,33 +1899,33 @@
       <c r="N45" s="10"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="6" t="s">
+      <c r="A46" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C46" s="6" t="s">
+      <c r="C46" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E46" s="6" t="s">
+      <c r="E46" s="1" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="6" t="s">
+      <c r="A47" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B47" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C47" s="14" t="s">
+      <c r="B47" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C47" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D47" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E47" s="6" t="s">
+      <c r="D47" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E47" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="F47" s="6" t="s">
+      <c r="F47" s="1" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1902,24 +1946,24 @@
       <c r="N48" s="10"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="6" t="s">
+      <c r="A49" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C49" s="6" t="s">
+      <c r="C49" s="1" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="6" t="s">
+      <c r="A50" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B50" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C50" s="6">
+      <c r="B50" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C50" s="1">
         <v>90</v>
       </c>
-      <c r="D50" s="6" t="s">
+      <c r="D50" s="1" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1940,15 +1984,15 @@
       <c r="N51" s="10"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="6" t="s">
-        <v>67</v>
+      <c r="A52" s="1" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="6" t="s">
+      <c r="A53" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B53" s="6" t="s">
+      <c r="B53" s="1" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1969,24 +2013,24 @@
       <c r="N54" s="10"/>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A55" s="6" t="s">
+      <c r="A55" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="C55" s="6" t="s">
+      <c r="C55" s="1" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A56" s="6" t="s">
+      <c r="A56" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B56" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C56" s="6" t="s">
+      <c r="B56" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C56" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D56" s="6" t="s">
+      <c r="D56" s="1" t="s">
         <v>32</v>
       </c>
     </row>
@@ -2007,15 +2051,15 @@
       <c r="N57" s="10"/>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A58" s="6" t="s">
+      <c r="A58" s="1" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A59" s="6" t="s">
+      <c r="A59" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B59" s="6" t="s">
+      <c r="B59" s="1" t="s">
         <v>32</v>
       </c>
     </row>
@@ -2035,16 +2079,45 @@
       <c r="M60" s="10"/>
       <c r="N60" s="10"/>
     </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A61" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A62" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A63" s="10"/>
+      <c r="B63" s="10"/>
+      <c r="C63" s="10"/>
+      <c r="D63" s="10"/>
+      <c r="E63" s="10"/>
+      <c r="F63" s="10"/>
+      <c r="G63" s="10"/>
+      <c r="H63" s="10"/>
+      <c r="I63" s="10"/>
+      <c r="J63" s="10"/>
+      <c r="K63" s="10"/>
+      <c r="L63" s="10"/>
+      <c r="M63" s="10"/>
+      <c r="N63" s="10"/>
+    </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A64" s="6" t="s">
+      <c r="A64" s="1" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A65" s="6" t="s">
+      <c r="A65" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B65" s="6" t="s">
+      <c r="B65" s="1" t="s">
         <v>32</v>
       </c>
     </row>
@@ -2065,15 +2138,15 @@
       <c r="N66" s="10"/>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A67" s="6" t="s">
+      <c r="A67" s="1" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A68" s="6" t="s">
+      <c r="A68" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B68" s="6" t="s">
+      <c r="B68" s="1" t="s">
         <v>32</v>
       </c>
     </row>
@@ -2094,70 +2167,82 @@
       <c r="N69" s="10"/>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A70" s="6" t="s">
+      <c r="A70" s="1" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A71" s="6" t="s">
+      <c r="A71" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B71" s="6" t="s">
+      <c r="B71" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A72" s="13"/>
-      <c r="B72" s="13"/>
-      <c r="C72" s="13"/>
-      <c r="D72" s="13"/>
-      <c r="E72" s="13"/>
-      <c r="F72" s="13"/>
-      <c r="G72" s="13"/>
-      <c r="H72" s="13"/>
-      <c r="I72" s="13"/>
-      <c r="J72" s="13"/>
-      <c r="K72" s="13"/>
-      <c r="L72" s="13"/>
-      <c r="M72" s="13"/>
-      <c r="N72" s="13"/>
+      <c r="A72" s="3"/>
+      <c r="B72" s="3"/>
+      <c r="C72" s="3"/>
+      <c r="D72" s="3"/>
+      <c r="E72" s="3"/>
+      <c r="F72" s="3"/>
+      <c r="G72" s="3"/>
+      <c r="H72" s="3"/>
+      <c r="I72" s="3"/>
+      <c r="J72" s="3"/>
+      <c r="K72" s="3"/>
+      <c r="L72" s="3"/>
+      <c r="M72" s="3"/>
+      <c r="N72" s="3"/>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A73" s="12"/>
-      <c r="B73" s="12"/>
-      <c r="C73" s="12"/>
-      <c r="D73" s="12"/>
-      <c r="E73" s="12"/>
-      <c r="F73" s="12"/>
-      <c r="G73" s="12" t="s">
+      <c r="A73" s="5"/>
+      <c r="B73" s="5"/>
+      <c r="C73" s="5"/>
+      <c r="D73" s="5"/>
+      <c r="E73" s="5"/>
+      <c r="F73" s="5"/>
+      <c r="G73" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="H73" s="12"/>
-      <c r="I73" s="12" t="s">
+      <c r="H73" s="5"/>
+      <c r="I73" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="J73" s="12"/>
-      <c r="K73" s="12" t="s">
+      <c r="J73" s="5"/>
+      <c r="K73" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="L73" s="12"/>
-      <c r="M73" s="12" t="s">
+      <c r="L73" s="5"/>
+      <c r="M73" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="N73" s="12"/>
+      <c r="N73" s="5"/>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="H75" s="6" t="s">
+      <c r="H75" s="1" t="s">
         <v>90</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="33">
-    <mergeCell ref="A54:N54"/>
-    <mergeCell ref="A66:N66"/>
-    <mergeCell ref="A69:N69"/>
-    <mergeCell ref="A57:N57"/>
-    <mergeCell ref="A60:N60"/>
+  <mergeCells count="34">
+    <mergeCell ref="C2:N2"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="G3:J3"/>
+    <mergeCell ref="K3:N3"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A35:N35"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="A5:N5"/>
+    <mergeCell ref="A11:N11"/>
+    <mergeCell ref="A14:N14"/>
+    <mergeCell ref="A17:N17"/>
+    <mergeCell ref="A20:N20"/>
+    <mergeCell ref="A23:N23"/>
+    <mergeCell ref="A26:N26"/>
+    <mergeCell ref="A29:N29"/>
+    <mergeCell ref="A32:N32"/>
     <mergeCell ref="A45:N45"/>
     <mergeCell ref="A48:N48"/>
     <mergeCell ref="A51:N51"/>
@@ -2169,23 +2254,12 @@
     <mergeCell ref="E43:F43"/>
     <mergeCell ref="G43:J43"/>
     <mergeCell ref="K43:N43"/>
-    <mergeCell ref="A20:N20"/>
-    <mergeCell ref="A23:N23"/>
-    <mergeCell ref="A26:N26"/>
-    <mergeCell ref="A29:N29"/>
-    <mergeCell ref="A32:N32"/>
-    <mergeCell ref="A35:N35"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="A5:N5"/>
-    <mergeCell ref="A11:N11"/>
-    <mergeCell ref="A14:N14"/>
-    <mergeCell ref="A17:N17"/>
-    <mergeCell ref="C2:N2"/>
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="G3:J3"/>
-    <mergeCell ref="K3:N3"/>
-    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A54:N54"/>
+    <mergeCell ref="A66:N66"/>
+    <mergeCell ref="A69:N69"/>
+    <mergeCell ref="A57:N57"/>
+    <mergeCell ref="A60:N60"/>
+    <mergeCell ref="A63:N63"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/Robot/АЛКУ_СВОДКА.xlsx
+++ b/Robot/АЛКУ_СВОДКА.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\SW001-ALKU\Robot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42F52439-260F-4D22-8C55-703779E6DA8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A596B0D-D0DD-48E6-B7E3-D5409D606D64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13080" yWindow="0" windowWidth="10056" windowHeight="12336" xr2:uid="{59D0C2ED-A381-469C-98D8-E3CEFE125B51}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{59D0C2ED-A381-469C-98D8-E3CEFE125B51}"/>
   </bookViews>
   <sheets>
     <sheet name="Общий графсет" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="102">
   <si>
     <t>Графсеты проекта АЛКУ</t>
   </si>
@@ -340,6 +340,9 @@
   </si>
   <si>
     <t>Пауза</t>
+  </si>
+  <si>
+    <t>Проверка программы</t>
   </si>
 </sst>
 </file>
@@ -437,6 +440,9 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -447,18 +453,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -795,56 +798,56 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16984AE6-47A2-4200-8C2D-12013DD9AE58}">
-  <dimension ref="A1:H38"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H40"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="44.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="44.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="33.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="33.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="33.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="33.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="G2" s="7" t="s">
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="G2" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="H2" s="7"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="6" t="s">
+      <c r="H2" s="8"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="G3" s="6" t="s">
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="G3" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="H3" s="6"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H3" s="7"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -864,7 +867,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>0</v>
       </c>
@@ -878,7 +881,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>1</v>
       </c>
@@ -892,7 +895,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2</v>
       </c>
@@ -906,7 +909,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>3</v>
       </c>
@@ -920,7 +923,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>4</v>
       </c>
@@ -934,19 +937,19 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>5</v>
       </c>
       <c r="B10" t="s">
         <v>27</v>
       </c>
-      <c r="G10" s="8" t="s">
+      <c r="G10" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="H10" s="8"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H10" s="9"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>6</v>
       </c>
@@ -960,7 +963,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>7</v>
       </c>
@@ -974,7 +977,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>8</v>
       </c>
@@ -988,7 +991,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>9</v>
       </c>
@@ -996,7 +999,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>100</v>
       </c>
@@ -1004,7 +1007,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>101</v>
       </c>
@@ -1012,7 +1015,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>102</v>
       </c>
@@ -1020,7 +1023,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>103</v>
       </c>
@@ -1028,7 +1031,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>104</v>
       </c>
@@ -1036,7 +1039,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>105</v>
       </c>
@@ -1044,152 +1047,168 @@
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21">
+        <v>106</v>
+      </c>
+      <c r="B21" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22">
         <v>255</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B22" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="6" t="s">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B23" s="6"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>2</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B25" t="s">
         <v>3</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C25" t="s">
         <v>4</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D25" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26">
         <v>0</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B26" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27">
         <v>1</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B27" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28">
         <v>2</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B28" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29">
         <v>3</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B29" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30">
         <v>4</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B30" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31">
         <v>5</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B31" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32">
         <v>6</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B32" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33">
         <v>100</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B33" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34">
         <v>101</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B34" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35">
         <v>102</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B35" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36">
         <v>103</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B36" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37">
         <v>104</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B37" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38">
         <v>105</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B38" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>106</v>
+      </c>
+      <c r="B39" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40">
         <v>255</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B40" t="s">
         <v>99</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A24:D24"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="G3:H3"/>
@@ -1203,26 +1222,26 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC90564D-037B-4C5E-8F1F-5400BED3BBC8}">
   <dimension ref="A1:N75"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="1.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="1.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="1.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="1.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="1.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="1.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="1.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="29.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="1.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="1.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="1.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="1.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="1.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="1.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>19</v>
       </c>
@@ -1240,53 +1259,53 @@
       <c r="M1" s="11"/>
       <c r="N1" s="11"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B2" s="2"/>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
-      <c r="L2" s="12"/>
-      <c r="M2" s="12"/>
-      <c r="N2" s="12"/>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3" s="13" t="s">
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13" t="s">
+      <c r="B3" s="12"/>
+      <c r="C3" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13" t="s">
+      <c r="D3" s="12"/>
+      <c r="E3" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13" t="s">
+      <c r="F3" s="12"/>
+      <c r="G3" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13" t="s">
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="L3" s="13"/>
-      <c r="M3" s="13"/>
-      <c r="N3" s="13"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="L3" s="12"/>
+      <c r="M3" s="12"/>
+      <c r="N3" s="12"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>31</v>
       </c>
@@ -1330,23 +1349,23 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A5" s="10"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="10"/>
-      <c r="L5" s="10"/>
-      <c r="M5" s="10"/>
-      <c r="N5" s="10"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="13"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="13"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="13"/>
+      <c r="L5" s="13"/>
+      <c r="M5" s="13"/>
+      <c r="N5" s="13"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>41</v>
       </c>
@@ -1357,7 +1376,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>43</v>
       </c>
@@ -1377,7 +1396,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>43</v>
       </c>
@@ -1397,7 +1416,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>43</v>
       </c>
@@ -1417,7 +1436,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>43</v>
       </c>
@@ -1437,23 +1456,23 @@
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="10"/>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="10"/>
-      <c r="M11" s="10"/>
-      <c r="N11" s="10"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="13"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="13"/>
+      <c r="J11" s="13"/>
+      <c r="K11" s="13"/>
+      <c r="L11" s="13"/>
+      <c r="M11" s="13"/>
+      <c r="N11" s="13"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>51</v>
       </c>
@@ -1461,7 +1480,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>53</v>
       </c>
@@ -1475,23 +1494,23 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="10"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="10"/>
-      <c r="K14" s="10"/>
-      <c r="L14" s="10"/>
-      <c r="M14" s="10"/>
-      <c r="N14" s="10"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="13"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="13"/>
+      <c r="J14" s="13"/>
+      <c r="K14" s="13"/>
+      <c r="L14" s="13"/>
+      <c r="M14" s="13"/>
+      <c r="N14" s="13"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>54</v>
       </c>
@@ -1505,7 +1524,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>58</v>
       </c>
@@ -1531,28 +1550,28 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="10"/>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10"/>
-      <c r="I17" s="10"/>
-      <c r="J17" s="10"/>
-      <c r="K17" s="10"/>
-      <c r="L17" s="10"/>
-      <c r="M17" s="10"/>
-      <c r="N17" s="10"/>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" s="13"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="13"/>
+      <c r="H17" s="13"/>
+      <c r="I17" s="13"/>
+      <c r="J17" s="13"/>
+      <c r="K17" s="13"/>
+      <c r="L17" s="13"/>
+      <c r="M17" s="13"/>
+      <c r="N17" s="13"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>62</v>
       </c>
@@ -1560,28 +1579,28 @@
         <v>32</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="10"/>
-      <c r="B20" s="10"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="10"/>
-      <c r="I20" s="10"/>
-      <c r="J20" s="10"/>
-      <c r="K20" s="10"/>
-      <c r="L20" s="10"/>
-      <c r="M20" s="10"/>
-      <c r="N20" s="10"/>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A20" s="13"/>
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="13"/>
+      <c r="I20" s="13"/>
+      <c r="J20" s="13"/>
+      <c r="K20" s="13"/>
+      <c r="L20" s="13"/>
+      <c r="M20" s="13"/>
+      <c r="N20" s="13"/>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>65</v>
       </c>
@@ -1589,28 +1608,28 @@
         <v>32</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="10"/>
-      <c r="B23" s="10"/>
-      <c r="C23" s="10"/>
-      <c r="D23" s="10"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="10"/>
-      <c r="H23" s="10"/>
-      <c r="I23" s="10"/>
-      <c r="J23" s="10"/>
-      <c r="K23" s="10"/>
-      <c r="L23" s="10"/>
-      <c r="M23" s="10"/>
-      <c r="N23" s="10"/>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A23" s="13"/>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="13"/>
+      <c r="H23" s="13"/>
+      <c r="I23" s="13"/>
+      <c r="J23" s="13"/>
+      <c r="K23" s="13"/>
+      <c r="L23" s="13"/>
+      <c r="M23" s="13"/>
+      <c r="N23" s="13"/>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>66</v>
       </c>
@@ -1618,28 +1637,28 @@
         <v>32</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="10"/>
-      <c r="B26" s="10"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="10"/>
-      <c r="G26" s="10"/>
-      <c r="H26" s="10"/>
-      <c r="I26" s="10"/>
-      <c r="J26" s="10"/>
-      <c r="K26" s="10"/>
-      <c r="L26" s="10"/>
-      <c r="M26" s="10"/>
-      <c r="N26" s="10"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A26" s="13"/>
+      <c r="B26" s="13"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="13"/>
+      <c r="H26" s="13"/>
+      <c r="I26" s="13"/>
+      <c r="J26" s="13"/>
+      <c r="K26" s="13"/>
+      <c r="L26" s="13"/>
+      <c r="M26" s="13"/>
+      <c r="N26" s="13"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>68</v>
       </c>
@@ -1647,28 +1666,28 @@
         <v>32</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="10"/>
-      <c r="B29" s="10"/>
-      <c r="C29" s="10"/>
-      <c r="D29" s="10"/>
-      <c r="E29" s="10"/>
-      <c r="F29" s="10"/>
-      <c r="G29" s="10"/>
-      <c r="H29" s="10"/>
-      <c r="I29" s="10"/>
-      <c r="J29" s="10"/>
-      <c r="K29" s="10"/>
-      <c r="L29" s="10"/>
-      <c r="M29" s="10"/>
-      <c r="N29" s="10"/>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A29" s="13"/>
+      <c r="B29" s="13"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="13"/>
+      <c r="G29" s="13"/>
+      <c r="H29" s="13"/>
+      <c r="I29" s="13"/>
+      <c r="J29" s="13"/>
+      <c r="K29" s="13"/>
+      <c r="L29" s="13"/>
+      <c r="M29" s="13"/>
+      <c r="N29" s="13"/>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>72</v>
       </c>
@@ -1676,28 +1695,28 @@
         <v>32</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="10"/>
-      <c r="B32" s="10"/>
-      <c r="C32" s="10"/>
-      <c r="D32" s="10"/>
-      <c r="E32" s="10"/>
-      <c r="F32" s="10"/>
-      <c r="G32" s="10"/>
-      <c r="H32" s="10"/>
-      <c r="I32" s="10"/>
-      <c r="J32" s="10"/>
-      <c r="K32" s="10"/>
-      <c r="L32" s="10"/>
-      <c r="M32" s="10"/>
-      <c r="N32" s="10"/>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="13"/>
+      <c r="B32" s="13"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="13"/>
+      <c r="G32" s="13"/>
+      <c r="H32" s="13"/>
+      <c r="I32" s="13"/>
+      <c r="J32" s="13"/>
+      <c r="K32" s="13"/>
+      <c r="L32" s="13"/>
+      <c r="M32" s="13"/>
+      <c r="N32" s="13"/>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>73</v>
       </c>
@@ -1705,28 +1724,28 @@
         <v>32</v>
       </c>
     </row>
-    <row r="35" spans="1:14" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="10"/>
-      <c r="B35" s="10"/>
-      <c r="C35" s="10"/>
-      <c r="D35" s="10"/>
-      <c r="E35" s="10"/>
-      <c r="F35" s="10"/>
-      <c r="G35" s="10"/>
-      <c r="H35" s="10"/>
-      <c r="I35" s="10"/>
-      <c r="J35" s="10"/>
-      <c r="K35" s="10"/>
-      <c r="L35" s="10"/>
-      <c r="M35" s="10"/>
-      <c r="N35" s="10"/>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:14" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="13"/>
+      <c r="B35" s="13"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="13"/>
+      <c r="F35" s="13"/>
+      <c r="G35" s="13"/>
+      <c r="H35" s="13"/>
+      <c r="I35" s="13"/>
+      <c r="J35" s="13"/>
+      <c r="K35" s="13"/>
+      <c r="L35" s="13"/>
+      <c r="M35" s="13"/>
+      <c r="N35" s="13"/>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>74</v>
       </c>
@@ -1734,23 +1753,23 @@
         <v>32</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="10"/>
-      <c r="B38" s="10"/>
-      <c r="C38" s="10"/>
-      <c r="D38" s="10"/>
-      <c r="E38" s="10"/>
-      <c r="F38" s="10"/>
-      <c r="G38" s="10"/>
-      <c r="H38" s="10"/>
-      <c r="I38" s="10"/>
-      <c r="J38" s="10"/>
-      <c r="K38" s="10"/>
-      <c r="L38" s="10"/>
-      <c r="M38" s="10"/>
-      <c r="N38" s="10"/>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A38" s="13"/>
+      <c r="B38" s="13"/>
+      <c r="C38" s="13"/>
+      <c r="D38" s="13"/>
+      <c r="E38" s="13"/>
+      <c r="F38" s="13"/>
+      <c r="G38" s="13"/>
+      <c r="H38" s="13"/>
+      <c r="I38" s="13"/>
+      <c r="J38" s="13"/>
+      <c r="K38" s="13"/>
+      <c r="L38" s="13"/>
+      <c r="M38" s="13"/>
+      <c r="N38" s="13"/>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="5"/>
       <c r="B39" s="5"/>
       <c r="C39" s="5"/>
@@ -1774,7 +1793,7 @@
       </c>
       <c r="N39" s="5"/>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="11" t="s">
         <v>20</v>
       </c>
@@ -1792,53 +1811,53 @@
       <c r="M41" s="11"/>
       <c r="N41" s="11"/>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B42" s="2"/>
-      <c r="C42" s="12" t="s">
+      <c r="C42" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="D42" s="12"/>
-      <c r="E42" s="12"/>
-      <c r="F42" s="12"/>
-      <c r="G42" s="12"/>
-      <c r="H42" s="12"/>
-      <c r="I42" s="12"/>
-      <c r="J42" s="12"/>
-      <c r="K42" s="12"/>
-      <c r="L42" s="12"/>
-      <c r="M42" s="12"/>
-      <c r="N42" s="12"/>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A43" s="13" t="s">
+      <c r="D42" s="10"/>
+      <c r="E42" s="10"/>
+      <c r="F42" s="10"/>
+      <c r="G42" s="10"/>
+      <c r="H42" s="10"/>
+      <c r="I42" s="10"/>
+      <c r="J42" s="10"/>
+      <c r="K42" s="10"/>
+      <c r="L42" s="10"/>
+      <c r="M42" s="10"/>
+      <c r="N42" s="10"/>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A43" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="B43" s="13"/>
-      <c r="C43" s="13" t="s">
+      <c r="B43" s="12"/>
+      <c r="C43" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="13"/>
-      <c r="E43" s="13" t="s">
+      <c r="D43" s="12"/>
+      <c r="E43" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="F43" s="13"/>
-      <c r="G43" s="13" t="s">
+      <c r="F43" s="12"/>
+      <c r="G43" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="H43" s="13"/>
-      <c r="I43" s="13"/>
-      <c r="J43" s="13"/>
-      <c r="K43" s="13" t="s">
+      <c r="H43" s="12"/>
+      <c r="I43" s="12"/>
+      <c r="J43" s="12"/>
+      <c r="K43" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="L43" s="13"/>
-      <c r="M43" s="13"/>
-      <c r="N43" s="13"/>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="L43" s="12"/>
+      <c r="M43" s="12"/>
+      <c r="N43" s="12"/>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>31</v>
       </c>
@@ -1882,23 +1901,23 @@
         <v>32</v>
       </c>
     </row>
-    <row r="45" spans="1:14" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="10"/>
-      <c r="B45" s="10"/>
-      <c r="C45" s="10"/>
-      <c r="D45" s="10"/>
-      <c r="E45" s="10"/>
-      <c r="F45" s="10"/>
-      <c r="G45" s="10"/>
-      <c r="H45" s="10"/>
-      <c r="I45" s="10"/>
-      <c r="J45" s="10"/>
-      <c r="K45" s="10"/>
-      <c r="L45" s="10"/>
-      <c r="M45" s="10"/>
-      <c r="N45" s="10"/>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:14" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="13"/>
+      <c r="B45" s="13"/>
+      <c r="C45" s="13"/>
+      <c r="D45" s="13"/>
+      <c r="E45" s="13"/>
+      <c r="F45" s="13"/>
+      <c r="G45" s="13"/>
+      <c r="H45" s="13"/>
+      <c r="I45" s="13"/>
+      <c r="J45" s="13"/>
+      <c r="K45" s="13"/>
+      <c r="L45" s="13"/>
+      <c r="M45" s="13"/>
+      <c r="N45" s="13"/>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>41</v>
       </c>
@@ -1909,7 +1928,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>43</v>
       </c>
@@ -1929,23 +1948,23 @@
         <v>32</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="10"/>
-      <c r="B48" s="10"/>
-      <c r="C48" s="10"/>
-      <c r="D48" s="10"/>
-      <c r="E48" s="10"/>
-      <c r="F48" s="10"/>
-      <c r="G48" s="10"/>
-      <c r="H48" s="10"/>
-      <c r="I48" s="10"/>
-      <c r="J48" s="10"/>
-      <c r="K48" s="10"/>
-      <c r="L48" s="10"/>
-      <c r="M48" s="10"/>
-      <c r="N48" s="10"/>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A48" s="13"/>
+      <c r="B48" s="13"/>
+      <c r="C48" s="13"/>
+      <c r="D48" s="13"/>
+      <c r="E48" s="13"/>
+      <c r="F48" s="13"/>
+      <c r="G48" s="13"/>
+      <c r="H48" s="13"/>
+      <c r="I48" s="13"/>
+      <c r="J48" s="13"/>
+      <c r="K48" s="13"/>
+      <c r="L48" s="13"/>
+      <c r="M48" s="13"/>
+      <c r="N48" s="13"/>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>51</v>
       </c>
@@ -1953,7 +1972,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>53</v>
       </c>
@@ -1967,28 +1986,28 @@
         <v>32</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A51" s="10"/>
-      <c r="B51" s="10"/>
-      <c r="C51" s="10"/>
-      <c r="D51" s="10"/>
-      <c r="E51" s="10"/>
-      <c r="F51" s="10"/>
-      <c r="G51" s="10"/>
-      <c r="H51" s="10"/>
-      <c r="I51" s="10"/>
-      <c r="J51" s="10"/>
-      <c r="K51" s="10"/>
-      <c r="L51" s="10"/>
-      <c r="M51" s="10"/>
-      <c r="N51" s="10"/>
-    </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A51" s="13"/>
+      <c r="B51" s="13"/>
+      <c r="C51" s="13"/>
+      <c r="D51" s="13"/>
+      <c r="E51" s="13"/>
+      <c r="F51" s="13"/>
+      <c r="G51" s="13"/>
+      <c r="H51" s="13"/>
+      <c r="I51" s="13"/>
+      <c r="J51" s="13"/>
+      <c r="K51" s="13"/>
+      <c r="L51" s="13"/>
+      <c r="M51" s="13"/>
+      <c r="N51" s="13"/>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>89</v>
       </c>
@@ -1996,23 +2015,23 @@
         <v>32</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A54" s="10"/>
-      <c r="B54" s="10"/>
-      <c r="C54" s="10"/>
-      <c r="D54" s="10"/>
-      <c r="E54" s="10"/>
-      <c r="F54" s="10"/>
-      <c r="G54" s="10"/>
-      <c r="H54" s="10"/>
-      <c r="I54" s="10"/>
-      <c r="J54" s="10"/>
-      <c r="K54" s="10"/>
-      <c r="L54" s="10"/>
-      <c r="M54" s="10"/>
-      <c r="N54" s="10"/>
-    </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A54" s="13"/>
+      <c r="B54" s="13"/>
+      <c r="C54" s="13"/>
+      <c r="D54" s="13"/>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
+      <c r="K54" s="13"/>
+      <c r="L54" s="13"/>
+      <c r="M54" s="13"/>
+      <c r="N54" s="13"/>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>93</v>
       </c>
@@ -2020,7 +2039,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>92</v>
       </c>
@@ -2034,28 +2053,28 @@
         <v>32</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A57" s="10"/>
-      <c r="B57" s="10"/>
-      <c r="C57" s="10"/>
-      <c r="D57" s="10"/>
-      <c r="E57" s="10"/>
-      <c r="F57" s="10"/>
-      <c r="G57" s="10"/>
-      <c r="H57" s="10"/>
-      <c r="I57" s="10"/>
-      <c r="J57" s="10"/>
-      <c r="K57" s="10"/>
-      <c r="L57" s="10"/>
-      <c r="M57" s="10"/>
-      <c r="N57" s="10"/>
-    </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A57" s="13"/>
+      <c r="B57" s="13"/>
+      <c r="C57" s="13"/>
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="13"/>
+      <c r="K57" s="13"/>
+      <c r="L57" s="13"/>
+      <c r="M57" s="13"/>
+      <c r="N57" s="13"/>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>95</v>
       </c>
@@ -2063,28 +2082,28 @@
         <v>32</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A60" s="10"/>
-      <c r="B60" s="10"/>
-      <c r="C60" s="10"/>
-      <c r="D60" s="10"/>
-      <c r="E60" s="10"/>
-      <c r="F60" s="10"/>
-      <c r="G60" s="10"/>
-      <c r="H60" s="10"/>
-      <c r="I60" s="10"/>
-      <c r="J60" s="10"/>
-      <c r="K60" s="10"/>
-      <c r="L60" s="10"/>
-      <c r="M60" s="10"/>
-      <c r="N60" s="10"/>
-    </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A60" s="13"/>
+      <c r="B60" s="13"/>
+      <c r="C60" s="13"/>
+      <c r="D60" s="13"/>
+      <c r="E60" s="13"/>
+      <c r="F60" s="13"/>
+      <c r="G60" s="13"/>
+      <c r="H60" s="13"/>
+      <c r="I60" s="13"/>
+      <c r="J60" s="13"/>
+      <c r="K60" s="13"/>
+      <c r="L60" s="13"/>
+      <c r="M60" s="13"/>
+      <c r="N60" s="13"/>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>97</v>
       </c>
@@ -2092,28 +2111,28 @@
         <v>32</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A63" s="10"/>
-      <c r="B63" s="10"/>
-      <c r="C63" s="10"/>
-      <c r="D63" s="10"/>
-      <c r="E63" s="10"/>
-      <c r="F63" s="10"/>
-      <c r="G63" s="10"/>
-      <c r="H63" s="10"/>
-      <c r="I63" s="10"/>
-      <c r="J63" s="10"/>
-      <c r="K63" s="10"/>
-      <c r="L63" s="10"/>
-      <c r="M63" s="10"/>
-      <c r="N63" s="10"/>
-    </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A63" s="13"/>
+      <c r="B63" s="13"/>
+      <c r="C63" s="13"/>
+      <c r="D63" s="13"/>
+      <c r="E63" s="13"/>
+      <c r="F63" s="13"/>
+      <c r="G63" s="13"/>
+      <c r="H63" s="13"/>
+      <c r="I63" s="13"/>
+      <c r="J63" s="13"/>
+      <c r="K63" s="13"/>
+      <c r="L63" s="13"/>
+      <c r="M63" s="13"/>
+      <c r="N63" s="13"/>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>72</v>
       </c>
@@ -2121,28 +2140,28 @@
         <v>32</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A66" s="10"/>
-      <c r="B66" s="10"/>
-      <c r="C66" s="10"/>
-      <c r="D66" s="10"/>
-      <c r="E66" s="10"/>
-      <c r="F66" s="10"/>
-      <c r="G66" s="10"/>
-      <c r="H66" s="10"/>
-      <c r="I66" s="10"/>
-      <c r="J66" s="10"/>
-      <c r="K66" s="10"/>
-      <c r="L66" s="10"/>
-      <c r="M66" s="10"/>
-      <c r="N66" s="10"/>
-    </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A66" s="13"/>
+      <c r="B66" s="13"/>
+      <c r="C66" s="13"/>
+      <c r="D66" s="13"/>
+      <c r="E66" s="13"/>
+      <c r="F66" s="13"/>
+      <c r="G66" s="13"/>
+      <c r="H66" s="13"/>
+      <c r="I66" s="13"/>
+      <c r="J66" s="13"/>
+      <c r="K66" s="13"/>
+      <c r="L66" s="13"/>
+      <c r="M66" s="13"/>
+      <c r="N66" s="13"/>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>73</v>
       </c>
@@ -2150,28 +2169,28 @@
         <v>32</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A69" s="10"/>
-      <c r="B69" s="10"/>
-      <c r="C69" s="10"/>
-      <c r="D69" s="10"/>
-      <c r="E69" s="10"/>
-      <c r="F69" s="10"/>
-      <c r="G69" s="10"/>
-      <c r="H69" s="10"/>
-      <c r="I69" s="10"/>
-      <c r="J69" s="10"/>
-      <c r="K69" s="10"/>
-      <c r="L69" s="10"/>
-      <c r="M69" s="10"/>
-      <c r="N69" s="10"/>
-    </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A69" s="13"/>
+      <c r="B69" s="13"/>
+      <c r="C69" s="13"/>
+      <c r="D69" s="13"/>
+      <c r="E69" s="13"/>
+      <c r="F69" s="13"/>
+      <c r="G69" s="13"/>
+      <c r="H69" s="13"/>
+      <c r="I69" s="13"/>
+      <c r="J69" s="13"/>
+      <c r="K69" s="13"/>
+      <c r="L69" s="13"/>
+      <c r="M69" s="13"/>
+      <c r="N69" s="13"/>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>74</v>
       </c>
@@ -2179,7 +2198,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" s="3"/>
       <c r="B72" s="3"/>
       <c r="C72" s="3"/>
@@ -2195,7 +2214,7 @@
       <c r="M72" s="3"/>
       <c r="N72" s="3"/>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" s="5"/>
       <c r="B73" s="5"/>
       <c r="C73" s="5"/>
@@ -2219,18 +2238,30 @@
       </c>
       <c r="N73" s="5"/>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="H75" s="1" t="s">
         <v>90</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="C2:N2"/>
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="G3:J3"/>
-    <mergeCell ref="K3:N3"/>
-    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A54:N54"/>
+    <mergeCell ref="A66:N66"/>
+    <mergeCell ref="A69:N69"/>
+    <mergeCell ref="A57:N57"/>
+    <mergeCell ref="A60:N60"/>
+    <mergeCell ref="A63:N63"/>
+    <mergeCell ref="A45:N45"/>
+    <mergeCell ref="A48:N48"/>
+    <mergeCell ref="A51:N51"/>
+    <mergeCell ref="A38:N38"/>
+    <mergeCell ref="A41:N41"/>
+    <mergeCell ref="C42:N42"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="G43:J43"/>
+    <mergeCell ref="K43:N43"/>
     <mergeCell ref="A35:N35"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="E3:F3"/>
@@ -2243,23 +2274,11 @@
     <mergeCell ref="A26:N26"/>
     <mergeCell ref="A29:N29"/>
     <mergeCell ref="A32:N32"/>
-    <mergeCell ref="A45:N45"/>
-    <mergeCell ref="A48:N48"/>
-    <mergeCell ref="A51:N51"/>
-    <mergeCell ref="A38:N38"/>
-    <mergeCell ref="A41:N41"/>
-    <mergeCell ref="C42:N42"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="E43:F43"/>
-    <mergeCell ref="G43:J43"/>
-    <mergeCell ref="K43:N43"/>
-    <mergeCell ref="A54:N54"/>
-    <mergeCell ref="A66:N66"/>
-    <mergeCell ref="A69:N69"/>
-    <mergeCell ref="A57:N57"/>
-    <mergeCell ref="A60:N60"/>
-    <mergeCell ref="A63:N63"/>
+    <mergeCell ref="C2:N2"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="G3:J3"/>
+    <mergeCell ref="K3:N3"/>
+    <mergeCell ref="A3:B3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
